--- a/product_selector_out/STM32H563-573.xlsx
+++ b/product_selector_out/STM32H563-573.xlsx
@@ -8266,9 +8266,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX12" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY12" s="6" t="inlineStr">
@@ -8603,9 +8603,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY13" s="6" t="inlineStr">
@@ -8940,9 +8940,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY14" s="6" t="inlineStr">
@@ -9277,9 +9277,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX15" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY15" s="6" t="inlineStr">
@@ -9614,9 +9614,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX16" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY16" s="6" t="inlineStr">
@@ -9951,9 +9951,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX17" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX17" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY17" s="6" t="inlineStr">
@@ -10288,9 +10288,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX18" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY18" s="6" t="inlineStr">
@@ -10625,9 +10625,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX19" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY19" s="6" t="inlineStr">
@@ -10962,9 +10962,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX20" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX20" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY20" s="6" t="inlineStr">
@@ -11299,9 +11299,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX21" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX21" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY21" s="6" t="inlineStr">
@@ -11636,9 +11636,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX22" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY22" s="6" t="inlineStr">
@@ -11973,9 +11973,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX23" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY23" s="6" t="inlineStr">
@@ -12310,9 +12310,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX24" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX24" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY24" s="6" t="inlineStr">
@@ -12647,9 +12647,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX25" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX25" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY25" s="6" t="inlineStr">
@@ -12984,9 +12984,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX26" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX26" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY26" s="6" t="inlineStr">
@@ -13321,9 +13321,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX27" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX27" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY27" s="6" t="inlineStr">
@@ -13658,9 +13658,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX28" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX28" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY28" s="6" t="inlineStr">
@@ -13995,9 +13995,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX29" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX29" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY29" s="6" t="inlineStr">
@@ -14332,9 +14332,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX30" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX30" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY30" s="6" t="inlineStr">
@@ -14438,7 +14438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -14487,19 +14487,19 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STM32H563IG</t>
+          <t>STM32H563LI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -14509,14 +14509,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STM32H563ZI</t>
+          <t>STM32H563IG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -14531,19 +14531,19 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STM32H573MI</t>
+          <t>STM32H563IG</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -14553,14 +14553,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STM32H573RI</t>
+          <t>STM32H563ZI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -14575,19 +14575,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STM32H563MI</t>
+          <t>STM32H563ZI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -14597,14 +14597,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STM32H563RG</t>
+          <t>STM32H573MI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -14619,19 +14619,19 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STM32H573ZI</t>
+          <t>STM32H573MI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -14641,14 +14641,14 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STM32H563ZG</t>
+          <t>STM32H573RI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -14663,19 +14663,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STM32H573II</t>
+          <t>STM32H573RI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -14685,14 +14685,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STM32H563VG</t>
+          <t>STM32H563MI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -14707,19 +14707,19 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STM32H573VI</t>
+          <t>STM32H563MI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -14729,14 +14729,14 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STM32H563RI</t>
+          <t>STM32H563RG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -14751,19 +14751,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STM32H563VI</t>
+          <t>STM32H563RG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -14773,14 +14773,14 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STM32H573AI</t>
+          <t>STM32H573ZI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -14795,19 +14795,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>STM32H563AI</t>
+          <t>STM32H573ZI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -14817,14 +14817,14 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>STM32H563II</t>
+          <t>STM32H563ZG</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -14839,19 +14839,19 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>STM32H563AG</t>
+          <t>STM32H563ZG</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -14861,29 +14861,447 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>STM32H573II</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>STM32H573II</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>STM32H563VG</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>STM32H563VG</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>STM32H573VI</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>STM32H573VI</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>STM32H563RI</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>STM32H563RI</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>STM32H563VI</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>STM32H563VI</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>STM32H573AI</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>STM32H573AI</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>STM32H563AI</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>STM32H563AI</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>STM32H563II</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>STM32H563II</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>STM32H563AG</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>STM32H563AG</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>STM32H573LI</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>Supply Voltage (V) min</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>STM32H573LI</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>

--- a/product_selector_out/STM32H563-573.xlsx
+++ b/product_selector_out/STM32H563-573.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO30"/>
+  <dimension ref="A1:BP30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.8046875" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,8 @@
     <col width="21.765625" customWidth="1" min="64" max="64"/>
     <col width="18" customWidth="1" min="65" max="65"/>
     <col width="18" customWidth="1" min="66" max="66"/>
-    <col width="52" customWidth="1" min="67" max="67"/>
+    <col width="18" customWidth="1" min="67" max="67"/>
+    <col width="52" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -907,6 +908,11 @@
         </is>
       </c>
       <c r="BO10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BP10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -1004,6 +1010,7 @@
       <c r="BM11" s="2" t="n"/>
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
+      <c r="BP11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1338,6 +1345,11 @@
       </c>
       <c r="BO12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h562ag.pdf</t>
         </is>
       </c>
@@ -1675,6 +1687,11 @@
       </c>
       <c r="BO13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h562ag.pdf</t>
         </is>
       </c>
@@ -2012,6 +2029,11 @@
       </c>
       <c r="BO14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h562ag.pdf</t>
         </is>
       </c>
@@ -2349,6 +2371,11 @@
       </c>
       <c r="BO15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h573ai.pdf</t>
         </is>
       </c>
@@ -2686,6 +2713,11 @@
       </c>
       <c r="BO16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h573ai.pdf</t>
         </is>
       </c>
@@ -3023,6 +3055,11 @@
       </c>
       <c r="BO17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h562ag.pdf</t>
         </is>
       </c>
@@ -3360,6 +3397,11 @@
       </c>
       <c r="BO18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h562ag.pdf</t>
         </is>
       </c>
@@ -3697,6 +3739,11 @@
       </c>
       <c r="BO19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h573ai.pdf</t>
         </is>
       </c>
@@ -4034,6 +4081,11 @@
       </c>
       <c r="BO20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h562ag.pdf</t>
         </is>
       </c>
@@ -4371,6 +4423,11 @@
       </c>
       <c r="BO21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h573ai.pdf</t>
         </is>
       </c>
@@ -4708,6 +4765,11 @@
       </c>
       <c r="BO22" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h562ag.pdf</t>
         </is>
       </c>
@@ -5045,6 +5107,11 @@
       </c>
       <c r="BO23" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h573ai.pdf</t>
         </is>
       </c>
@@ -5382,6 +5449,11 @@
       </c>
       <c r="BO24" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h562ag.pdf</t>
         </is>
       </c>
@@ -5719,6 +5791,11 @@
       </c>
       <c r="BO25" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP25" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h562ag.pdf</t>
         </is>
       </c>
@@ -6056,6 +6133,11 @@
       </c>
       <c r="BO26" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP26" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h573ai.pdf</t>
         </is>
       </c>
@@ -6393,6 +6475,11 @@
       </c>
       <c r="BO27" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP27" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h562ag.pdf</t>
         </is>
       </c>
@@ -6730,6 +6817,11 @@
       </c>
       <c r="BO28" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP28" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h562ag.pdf</t>
         </is>
       </c>
@@ -7067,6 +7159,11 @@
       </c>
       <c r="BO29" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP29" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h562ag.pdf</t>
         </is>
       </c>
@@ -7404,12 +7501,17 @@
       </c>
       <c r="BO30" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP30" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h573ai.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="66">
+  <mergeCells count="67">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -7432,12 +7534,14 @@
     <mergeCell ref="Q10:Q11"/>
     <mergeCell ref="AR10:AR11"/>
     <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="A9:BP9"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="A1:BP8"/>
     <mergeCell ref="AV10:AV11"/>
     <mergeCell ref="BB10:BB11"/>
+    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BD10:BD11"/>
     <mergeCell ref="BM10:BM11"/>
-    <mergeCell ref="BD10:BD11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -7452,9 +7556,8 @@
     <mergeCell ref="BH10:BH11"/>
     <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
-    <mergeCell ref="A1:BO8"/>
+    <mergeCell ref="BP10:BP11"/>
     <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="A9:BO9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="I10:I11"/>
     <mergeCell ref="AL10:AL11"/>
@@ -7509,7 +7612,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO30"/>
+  <dimension ref="A1:BP30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7579,6 +7682,7 @@
     <col width="16" customWidth="1" min="65" max="65"/>
     <col width="16" customWidth="1" min="66" max="66"/>
     <col width="16" customWidth="1" min="67" max="67"/>
+    <col width="16" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7922,6 +8026,11 @@
         </is>
       </c>
       <c r="BO10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BP10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -8019,6 +8128,7 @@
       <c r="BM11" s="2" t="n"/>
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
+      <c r="BP11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -8351,7 +8461,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO12" s="6" t="inlineStr">
+      <c r="BO12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8688,7 +8803,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO13" s="6" t="inlineStr">
+      <c r="BO13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9025,7 +9145,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO14" s="6" t="inlineStr">
+      <c r="BO14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9362,7 +9487,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO15" s="6" t="inlineStr">
+      <c r="BO15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9699,7 +9829,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO16" s="6" t="inlineStr">
+      <c r="BO16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10036,7 +10171,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO17" s="6" t="inlineStr">
+      <c r="BO17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10373,7 +10513,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO18" s="6" t="inlineStr">
+      <c r="BO18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10710,7 +10855,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO19" s="6" t="inlineStr">
+      <c r="BO19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11047,7 +11197,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO20" s="6" t="inlineStr">
+      <c r="BO20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11384,7 +11539,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO21" s="6" t="inlineStr">
+      <c r="BO21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11721,7 +11881,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO22" s="6" t="inlineStr">
+      <c r="BO22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12058,7 +12223,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO23" s="6" t="inlineStr">
+      <c r="BO23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12395,7 +12565,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO24" s="6" t="inlineStr">
+      <c r="BO24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12732,7 +12907,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO25" s="6" t="inlineStr">
+      <c r="BO25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP25" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13069,7 +13249,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO26" s="6" t="inlineStr">
+      <c r="BO26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP26" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13406,7 +13591,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO27" s="6" t="inlineStr">
+      <c r="BO27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP27" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13743,7 +13933,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO28" s="6" t="inlineStr">
+      <c r="BO28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP28" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14080,7 +14275,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO29" s="6" t="inlineStr">
+      <c r="BO29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP29" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14417,7 +14617,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO30" s="6" t="inlineStr">
+      <c r="BO30" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP30" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14425,8 +14630,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BO9"/>
-    <mergeCell ref="A1:BO8"/>
+    <mergeCell ref="A1:BP8"/>
+    <mergeCell ref="A9:BP9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
